--- a/Data/National Accounts/PSA-18REOD_2018PSNA_Qrt.xlsx
+++ b/Data/National Accounts/PSA-18REOD_2018PSNA_Qrt.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28324"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\Shared drives\QNAP\NAP Dissemination\As of January 2026\Tables\Prelim Q4 2025\NAP Q1 2000 to Q4 2025\Qtr\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="I:\Shared drives\QNAP\NAP Dissemination\As of April 2026\Tables\NAP Q1 2000 to Q4 2025\Qtr\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D124D5A0-9E6C-45B9-9EEF-0BB281238346}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BAC02B64-1626-4748-9988-E6B2169B6964}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="794" xr2:uid="{736930C2-BFBB-46C3-AE9E-AECFC8C3145D}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="794" xr2:uid="{736930C2-BFBB-46C3-AE9E-AECFC8C3145D}"/>
   </bookViews>
   <sheets>
     <sheet name="REOD" sheetId="18" r:id="rId1"/>
@@ -685,10 +685,10 @@
     <t>Table 19.7 Gross Value Added in Real Estate and Ownership of Dwellings , by Industry</t>
   </si>
   <si>
-    <t>As of January 2026</t>
+    <t>Q1 2000 to Q4 2025</t>
   </si>
   <si>
-    <t>Q1 2000 to Q4 2025</t>
+    <t>As of April 2026</t>
   </si>
 </sst>
 </file>
@@ -737,10 +737,12 @@
       <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="12"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="12"/>
@@ -1205,7 +1207,7 @@
     </row>
     <row r="3" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="5" spans="1:179" x14ac:dyDescent="0.2">
@@ -1215,7 +1217,7 @@
     </row>
     <row r="6" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="7" spans="1:179" x14ac:dyDescent="0.2">
@@ -2001,22 +2003,22 @@
         <v>189886.8773609515</v>
       </c>
       <c r="CV12" s="18">
-        <v>204311.74026359257</v>
+        <v>204600.57584429131</v>
       </c>
       <c r="CW12" s="18">
-        <v>203440.80776692316</v>
+        <v>205457.74613975416</v>
       </c>
       <c r="CX12" s="18">
-        <v>194286.06714217673</v>
+        <v>194290.00197620993</v>
       </c>
       <c r="CY12" s="18">
         <v>210704.94865481317</v>
       </c>
       <c r="CZ12" s="18">
-        <v>219227.07331628472</v>
+        <v>220701.61695921939</v>
       </c>
       <c r="DA12" s="18">
-        <v>219670.39946743881</v>
+        <v>221017.2832523628</v>
       </c>
       <c r="DB12" s="8"/>
       <c r="DC12" s="8"/>
@@ -2392,7 +2394,7 @@
         <v>177597.72670989437</v>
       </c>
       <c r="CV13" s="18">
-        <v>179404.67657826995</v>
+        <v>179407.34352721344</v>
       </c>
       <c r="CW13" s="18">
         <v>176256.8611823098</v>
@@ -2963,22 +2965,22 @@
         <v>367484.60407084587</v>
       </c>
       <c r="CV15" s="19">
-        <v>383716.41684186249</v>
+        <v>384007.91937150474</v>
       </c>
       <c r="CW15" s="19">
-        <v>379697.66894923296</v>
+        <v>381714.607322064</v>
       </c>
       <c r="CX15" s="19">
-        <v>376017.74682600284</v>
+        <v>376021.68166003609</v>
       </c>
       <c r="CY15" s="19">
         <v>394909.50933878467</v>
       </c>
       <c r="CZ15" s="19">
-        <v>406754.22139033827</v>
+        <v>408228.76503327291</v>
       </c>
       <c r="DA15" s="19">
-        <v>404458.49209260603</v>
+        <v>405805.37587752996</v>
       </c>
       <c r="DB15" s="8"/>
       <c r="DC15" s="8"/>
@@ -3539,7 +3541,7 @@
     </row>
     <row r="22" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A22" s="3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="24" spans="1:179" x14ac:dyDescent="0.2">
@@ -3549,7 +3551,7 @@
     </row>
     <row r="25" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A25" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="26" spans="1:179" x14ac:dyDescent="0.2">
@@ -4335,22 +4337,22 @@
         <v>149419.15668608685</v>
       </c>
       <c r="CV31" s="18">
-        <v>164287.42201280617</v>
+        <v>164519.67520039756</v>
       </c>
       <c r="CW31" s="18">
-        <v>158054.03761687764</v>
+        <v>159621.00570430077</v>
       </c>
       <c r="CX31" s="18">
-        <v>147448.8067469708</v>
+        <v>147451.79299601831</v>
       </c>
       <c r="CY31" s="18">
         <v>164084.07506221434</v>
       </c>
       <c r="CZ31" s="18">
-        <v>173918.17655110281</v>
+        <v>175087.96793564694</v>
       </c>
       <c r="DA31" s="18">
-        <v>168567.01743981396</v>
+        <v>169600.56671642614</v>
       </c>
       <c r="DB31" s="8"/>
       <c r="DC31" s="8"/>
@@ -4726,7 +4728,7 @@
         <v>150531.11215960496</v>
       </c>
       <c r="CV32" s="18">
-        <v>150713.89269145762</v>
+        <v>150716.12439864318</v>
       </c>
       <c r="CW32" s="18">
         <v>148149.16581496713</v>
@@ -5297,22 +5299,22 @@
         <v>299950.26884569181</v>
       </c>
       <c r="CV34" s="19">
-        <v>315001.31470426382</v>
+        <v>315235.79959904077</v>
       </c>
       <c r="CW34" s="19">
-        <v>306203.20343184477</v>
+        <v>307770.1715192679</v>
       </c>
       <c r="CX34" s="19">
-        <v>299936.37282973214</v>
+        <v>299939.35907877964</v>
       </c>
       <c r="CY34" s="19">
         <v>317562.61678581603</v>
       </c>
       <c r="CZ34" s="19">
-        <v>327568.97351321817</v>
+        <v>328738.76489776233</v>
       </c>
       <c r="DA34" s="19">
-        <v>320107.33921111422</v>
+        <v>321140.88848772639</v>
       </c>
       <c r="DB34" s="8"/>
       <c r="DC34" s="8"/>
@@ -5881,7 +5883,7 @@
     </row>
     <row r="41" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A41" s="3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="CX41" s="4"/>
       <c r="CY41" s="4"/>
@@ -5909,7 +5911,7 @@
     </row>
     <row r="44" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A44" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="CS44" s="6"/>
       <c r="CT44" s="6"/>
@@ -6697,22 +6699,22 @@
         <v>18.815544554209083</v>
       </c>
       <c r="CR50" s="15">
-        <v>12.033898056648255</v>
+        <v>12.192280418627959</v>
       </c>
       <c r="CS50" s="15">
-        <v>6.8048339891842744</v>
+        <v>7.8637108705788421</v>
       </c>
       <c r="CT50" s="15">
-        <v>7.6922058840291641</v>
+        <v>7.694386951169264</v>
       </c>
       <c r="CU50" s="15">
         <v>10.963407046969891</v>
       </c>
       <c r="CV50" s="15">
-        <v>7.3002819287081309</v>
+        <v>7.8694994129349709</v>
       </c>
       <c r="CW50" s="15">
-        <v>7.9775497741384669</v>
+        <v>7.5731080501705321</v>
       </c>
       <c r="CX50" s="17"/>
       <c r="CY50" s="17"/>
@@ -7076,7 +7078,7 @@
         <v>5.1620211192349785</v>
       </c>
       <c r="CR51" s="15">
-        <v>4.8344252997718939</v>
+        <v>4.8359837210189056</v>
       </c>
       <c r="CS51" s="15">
         <v>4.5724287268197799</v>
@@ -7088,7 +7090,7 @@
         <v>3.7201117922355991</v>
       </c>
       <c r="CV51" s="15">
-        <v>4.5274580633576562</v>
+        <v>4.5259042284456115</v>
       </c>
       <c r="CW51" s="15">
         <v>4.8402265793404666</v>
@@ -7632,22 +7634,22 @@
         <v>11.80053979795666</v>
       </c>
       <c r="CR53" s="15">
-        <v>8.5485653546994627</v>
+        <v>8.6310277670464757</v>
       </c>
       <c r="CS53" s="15">
-        <v>5.756807461117603</v>
+        <v>6.3185832648688489</v>
       </c>
       <c r="CT53" s="15">
-        <v>5.9268968359323964</v>
+        <v>5.9280053069080907</v>
       </c>
       <c r="CU53" s="15">
         <v>7.4628719037850288</v>
       </c>
       <c r="CV53" s="15">
-        <v>6.0038621068355695</v>
+        <v>6.307381811658928</v>
       </c>
       <c r="CW53" s="15">
-        <v>6.5211944049842714</v>
+        <v>6.3111990197272974</v>
       </c>
       <c r="CX53" s="17"/>
       <c r="CY53" s="17"/>
@@ -8212,7 +8214,7 @@
     </row>
     <row r="60" spans="1:175" x14ac:dyDescent="0.2">
       <c r="A60" s="3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="CX60" s="4"/>
       <c r="CY60" s="4"/>
@@ -8236,7 +8238,7 @@
     </row>
     <row r="63" spans="1:175" x14ac:dyDescent="0.2">
       <c r="A63" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="CX63" s="4"/>
       <c r="CY63" s="4"/>
@@ -9018,22 +9020,22 @@
         <v>13.817095533316959</v>
       </c>
       <c r="CR69" s="15">
-        <v>8.1469353587317386</v>
+        <v>8.2998227201473327</v>
       </c>
       <c r="CS69" s="15">
-        <v>3.9133365968470741</v>
+        <v>4.9435468006484768</v>
       </c>
       <c r="CT69" s="15">
-        <v>5.2584573612014367</v>
+        <v>5.2605891381548844</v>
       </c>
       <c r="CU69" s="15">
         <v>9.8146172829343783</v>
       </c>
       <c r="CV69" s="15">
-        <v>5.8621374785136737</v>
+        <v>6.4237257473164959</v>
       </c>
       <c r="CW69" s="15">
-        <v>6.6515098136371194</v>
+        <v>6.2520349173921232</v>
       </c>
       <c r="CX69" s="17"/>
       <c r="CY69" s="17"/>
@@ -9397,7 +9399,7 @@
         <v>2.2454618055610496</v>
       </c>
       <c r="CR70" s="15">
-        <v>2.1905020985510788</v>
+        <v>2.1920152920182261</v>
       </c>
       <c r="CS70" s="15">
         <v>2.1716578885816631</v>
@@ -9409,7 +9411,7 @@
         <v>1.9580201871302307</v>
       </c>
       <c r="CV70" s="15">
-        <v>1.9486619436405874</v>
+        <v>1.9471523535929123</v>
       </c>
       <c r="CW70" s="15">
         <v>2.289014546709339</v>
@@ -9952,22 +9954,22 @@
         <v>7.7000254194891795</v>
       </c>
       <c r="CR72" s="15">
-        <v>5.2127664704786127</v>
+        <v>5.2910861578049548</v>
       </c>
       <c r="CS72" s="15">
-        <v>3.0633126125131582</v>
+        <v>3.5907300922713716</v>
       </c>
       <c r="CT72" s="15">
-        <v>3.677727351319831</v>
+        <v>3.6787595952975352</v>
       </c>
       <c r="CU72" s="15">
         <v>5.8717560107221658</v>
       </c>
       <c r="CV72" s="15">
-        <v>3.9897163034869862</v>
+        <v>4.2834491881621517</v>
       </c>
       <c r="CW72" s="15">
-        <v>4.5408198292622473</v>
+        <v>4.3443836361580139</v>
       </c>
       <c r="CX72" s="17"/>
       <c r="CY72" s="17"/>
@@ -10527,7 +10529,7 @@
     </row>
     <row r="78" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A78" s="3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="CX78" s="4"/>
       <c r="CY78" s="4"/>
@@ -10551,7 +10553,7 @@
     </row>
     <row r="81" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A81" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="CX81" s="4"/>
       <c r="CY81" s="4"/>
@@ -11345,19 +11347,19 @@
         <v>127.08335502112548</v>
       </c>
       <c r="CV87" s="15">
-        <v>124.36237525698499</v>
+        <v>124.36237525698502</v>
       </c>
       <c r="CW87" s="15">
         <v>128.71598273247716</v>
       </c>
       <c r="CX87" s="15">
-        <v>131.76509964952169</v>
+        <v>131.76509964952166</v>
       </c>
       <c r="CY87" s="15">
         <v>128.4127960467352</v>
       </c>
       <c r="CZ87" s="15">
-        <v>126.05184671532517</v>
+        <v>126.05184671532518</v>
       </c>
       <c r="DA87" s="15">
         <v>130.31635891990027</v>
@@ -11736,7 +11738,7 @@
         <v>117.98074442019086</v>
       </c>
       <c r="CV88" s="15">
-        <v>119.03658871418594</v>
+        <v>119.03659561513284</v>
       </c>
       <c r="CW88" s="15">
         <v>118.97256404565123</v>
@@ -12307,22 +12309,22 @@
         <v>122.51517742759445</v>
       </c>
       <c r="CV90" s="15">
-        <v>121.81422709365873</v>
+        <v>121.81608810291775</v>
       </c>
       <c r="CW90" s="15">
-        <v>124.00186042917957</v>
+        <v>124.02586171290704</v>
       </c>
       <c r="CX90" s="15">
-        <v>125.36583785370392</v>
+        <v>125.36590156588061</v>
       </c>
       <c r="CY90" s="15">
         <v>124.35642247057568</v>
       </c>
       <c r="CZ90" s="15">
-        <v>124.17361053089016</v>
+        <v>124.18029408860009</v>
       </c>
       <c r="DA90" s="15">
-        <v>126.35089626166345</v>
+        <v>126.36365857630096</v>
       </c>
       <c r="DB90" s="8"/>
       <c r="DC90" s="8"/>
@@ -12523,7 +12525,7 @@
     </row>
     <row r="97" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A97" s="3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="99" spans="1:179" x14ac:dyDescent="0.2">
@@ -12533,7 +12535,7 @@
     </row>
     <row r="100" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A100" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="101" spans="1:179" x14ac:dyDescent="0.2">
@@ -13319,22 +13321,22 @@
         <v>51.67206333475238</v>
       </c>
       <c r="CV106" s="15">
-        <v>53.24550404831745</v>
+        <v>53.280301140444053</v>
       </c>
       <c r="CW106" s="15">
-        <v>53.579683101537292</v>
+        <v>53.824962995561584</v>
       </c>
       <c r="CX106" s="15">
-        <v>51.669387623898508</v>
+        <v>51.66989337382649</v>
       </c>
       <c r="CY106" s="15">
         <v>53.355248144722125</v>
       </c>
       <c r="CZ106" s="15">
-        <v>53.896692839950958</v>
+        <v>54.063220395855978</v>
       </c>
       <c r="DA106" s="15">
-        <v>54.312223321334642</v>
+        <v>54.463862824494647</v>
       </c>
       <c r="DB106" s="8"/>
       <c r="DC106" s="8"/>
@@ -13710,22 +13712,22 @@
         <v>48.32793666524762</v>
       </c>
       <c r="CV107" s="15">
-        <v>46.754495951682557</v>
+        <v>46.719698859555955</v>
       </c>
       <c r="CW107" s="15">
-        <v>46.420316898462715</v>
+        <v>46.175037004438408</v>
       </c>
       <c r="CX107" s="15">
-        <v>48.330612376101499</v>
+        <v>48.330106626173503</v>
       </c>
       <c r="CY107" s="15">
         <v>46.644751855277875</v>
       </c>
       <c r="CZ107" s="15">
-        <v>46.103307160049042</v>
+        <v>45.936779604144022</v>
       </c>
       <c r="DA107" s="15">
-        <v>45.687776678665351</v>
+        <v>45.536137175505367</v>
       </c>
       <c r="DB107" s="8"/>
       <c r="DC107" s="8"/>
@@ -14857,7 +14859,7 @@
     </row>
     <row r="116" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A116" s="3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="118" spans="1:179" x14ac:dyDescent="0.2">
@@ -14867,7 +14869,7 @@
     </row>
     <row r="119" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A119" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="120" spans="1:179" x14ac:dyDescent="0.2">
@@ -15653,22 +15655,22 @@
         <v>49.814643361081608</v>
       </c>
       <c r="CV125" s="15">
-        <v>52.154519471465058</v>
+        <v>52.189400889637461</v>
       </c>
       <c r="CW125" s="15">
-        <v>51.617369069118048</v>
+        <v>51.863702358273443</v>
       </c>
       <c r="CX125" s="15">
-        <v>49.16002862736309</v>
+        <v>49.160534799065772</v>
       </c>
       <c r="CY125" s="15">
         <v>51.669833408912503</v>
       </c>
       <c r="CZ125" s="15">
-        <v>53.093604893591916</v>
+        <v>53.26051766061093</v>
       </c>
       <c r="DA125" s="15">
-        <v>52.659529098969585</v>
+        <v>52.811888113994577</v>
       </c>
       <c r="DB125" s="8"/>
       <c r="DC125" s="8"/>
@@ -16044,22 +16046,22 @@
         <v>50.185356638918385</v>
       </c>
       <c r="CV126" s="15">
-        <v>47.845480528534942</v>
+        <v>47.810599110362531</v>
       </c>
       <c r="CW126" s="15">
-        <v>48.382630930881959</v>
+        <v>48.136297641726557</v>
       </c>
       <c r="CX126" s="15">
-        <v>50.839971372636917</v>
+        <v>50.839465200934228</v>
       </c>
       <c r="CY126" s="15">
         <v>48.33016659108749</v>
       </c>
       <c r="CZ126" s="15">
-        <v>46.906395106408084</v>
+        <v>46.739482339389063</v>
       </c>
       <c r="DA126" s="15">
-        <v>47.340470901030415</v>
+        <v>47.18811188600543</v>
       </c>
       <c r="DB126" s="8"/>
       <c r="DC126" s="8"/>

--- a/Data/National Accounts/PSA-18REOD_2018PSNA_Qrt.xlsx
+++ b/Data/National Accounts/PSA-18REOD_2018PSNA_Qrt.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28324"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="I:\Shared drives\QNAP\NAP Dissemination\As of April 2026\Tables\NAP Q1 2000 to Q4 2025\Qtr\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\Shared drives\QNAP\NAP Dissemination\As of May 2026\Tables\NAP Q1 2000 to Q1 2026\Qtr\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BAC02B64-1626-4748-9988-E6B2169B6964}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C7A8A01-8E71-485D-83FD-C55BD26AEF9D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="794" xr2:uid="{736930C2-BFBB-46C3-AE9E-AECFC8C3145D}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="794" xr2:uid="{736930C2-BFBB-46C3-AE9E-AECFC8C3145D}"/>
   </bookViews>
   <sheets>
     <sheet name="REOD" sheetId="18" r:id="rId1"/>
@@ -356,7 +356,7 @@
     <definedName name="pet">#REF!</definedName>
     <definedName name="plastic">#REF!</definedName>
     <definedName name="ply">#REF!</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">REOD!$A$1:$DA$131</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">REOD!$A$1:$DB$131</definedName>
     <definedName name="_xlnm.Print_Area">#REF!</definedName>
     <definedName name="PRINT_AREA_MI">#REF!</definedName>
     <definedName name="Print_Titles_MI">#REF!,#REF!</definedName>
@@ -530,7 +530,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="846" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="855" uniqueCount="54">
   <si>
     <t>National Accounts of the Philippines</t>
   </si>
@@ -685,10 +685,13 @@
     <t>Table 19.7 Gross Value Added in Real Estate and Ownership of Dwellings , by Industry</t>
   </si>
   <si>
-    <t>Q1 2000 to Q4 2025</t>
+    <t>Q1 2000 to Q1 2026</t>
   </si>
   <si>
-    <t>As of April 2026</t>
+    <t>As of May 2026</t>
+  </si>
+  <si>
+    <t>2025 - 2026</t>
   </si>
 </sst>
 </file>
@@ -1191,8 +1194,8 @@
   <sheetFormatPr defaultColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="49.28515625" style="3" customWidth="1"/>
-    <col min="2" max="105" width="13" style="3" customWidth="1"/>
-    <col min="106" max="16384" width="10" style="3"/>
+    <col min="2" max="106" width="13" style="3" customWidth="1"/>
+    <col min="107" max="16384" width="10" style="3"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:179" x14ac:dyDescent="0.2">
@@ -1383,6 +1386,9 @@
       <c r="CY9" s="20"/>
       <c r="CZ9" s="20"/>
       <c r="DA9" s="20"/>
+      <c r="DB9" s="20">
+        <v>2026</v>
+      </c>
     </row>
     <row r="10" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A10" s="5" t="s">
@@ -1699,6 +1705,9 @@
       </c>
       <c r="DA10" s="12" t="s">
         <v>5</v>
+      </c>
+      <c r="DB10" s="12" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="11" spans="1:179" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
@@ -2020,7 +2029,9 @@
       <c r="DA12" s="18">
         <v>221017.2832523628</v>
       </c>
-      <c r="DB12" s="8"/>
+      <c r="DB12" s="18">
+        <v>209954.43739119213</v>
+      </c>
       <c r="DC12" s="8"/>
       <c r="DD12" s="8"/>
       <c r="DE12" s="8"/>
@@ -2411,7 +2422,9 @@
       <c r="DA13" s="18">
         <v>184788.09262516719</v>
       </c>
-      <c r="DB13" s="8"/>
+      <c r="DB13" s="18">
+        <v>191651.17541377526</v>
+      </c>
       <c r="DC13" s="8"/>
       <c r="DD13" s="8"/>
       <c r="DE13" s="8"/>
@@ -2982,7 +2995,9 @@
       <c r="DA15" s="19">
         <v>405805.37587752996</v>
       </c>
-      <c r="DB15" s="8"/>
+      <c r="DB15" s="19">
+        <v>401605.61280496739</v>
+      </c>
       <c r="DC15" s="8"/>
       <c r="DD15" s="8"/>
       <c r="DE15" s="8"/>
@@ -3163,6 +3178,7 @@
       <c r="CY16" s="10"/>
       <c r="CZ16" s="10"/>
       <c r="DA16" s="10"/>
+      <c r="DB16" s="10"/>
     </row>
     <row r="17" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A17" s="11" t="s">
@@ -3717,6 +3733,9 @@
       <c r="CY28" s="20"/>
       <c r="CZ28" s="20"/>
       <c r="DA28" s="20"/>
+      <c r="DB28" s="20">
+        <v>2026</v>
+      </c>
     </row>
     <row r="29" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A29" s="5" t="s">
@@ -4033,6 +4052,9 @@
       </c>
       <c r="DA29" s="12" t="s">
         <v>5</v>
+      </c>
+      <c r="DB29" s="12" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="30" spans="1:179" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
@@ -4354,7 +4376,9 @@
       <c r="DA31" s="18">
         <v>169600.56671642614</v>
       </c>
-      <c r="DB31" s="8"/>
+      <c r="DB31" s="18">
+        <v>154785.20443143079</v>
+      </c>
       <c r="DC31" s="8"/>
       <c r="DD31" s="8"/>
       <c r="DE31" s="8"/>
@@ -4745,7 +4769,9 @@
       <c r="DA32" s="18">
         <v>151540.32177130025</v>
       </c>
-      <c r="DB32" s="8"/>
+      <c r="DB32" s="18">
+        <v>155076.18492327217</v>
+      </c>
       <c r="DC32" s="8"/>
       <c r="DD32" s="8"/>
       <c r="DE32" s="8"/>
@@ -5316,7 +5342,9 @@
       <c r="DA34" s="19">
         <v>321140.88848772639</v>
       </c>
-      <c r="DB34" s="8"/>
+      <c r="DB34" s="19">
+        <v>309861.38935470296</v>
+      </c>
       <c r="DC34" s="8"/>
       <c r="DD34" s="8"/>
       <c r="DE34" s="8"/>
@@ -5497,6 +5525,7 @@
       <c r="CY35" s="10"/>
       <c r="CZ35" s="10"/>
       <c r="DA35" s="10"/>
+      <c r="DB35" s="10"/>
     </row>
     <row r="36" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A36" s="11" t="s">
@@ -5608,7 +5637,7 @@
       <c r="CY37" s="7"/>
       <c r="CZ37" s="7"/>
       <c r="DA37" s="7"/>
-      <c r="DB37" s="8"/>
+      <c r="DB37" s="7"/>
       <c r="DC37" s="8"/>
       <c r="DD37" s="8"/>
       <c r="DE37" s="8"/>
@@ -5788,7 +5817,7 @@
       <c r="CY38" s="7"/>
       <c r="CZ38" s="7"/>
       <c r="DA38" s="7"/>
-      <c r="DB38" s="8"/>
+      <c r="DB38" s="7"/>
       <c r="DC38" s="8"/>
       <c r="DD38" s="8"/>
       <c r="DE38" s="8"/>
@@ -5871,6 +5900,7 @@
       <c r="CY39" s="4"/>
       <c r="CZ39" s="4"/>
       <c r="DA39" s="4"/>
+      <c r="DB39" s="4"/>
     </row>
     <row r="40" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A40" s="3" t="s">
@@ -5880,6 +5910,7 @@
       <c r="CY40" s="4"/>
       <c r="CZ40" s="4"/>
       <c r="DA40" s="4"/>
+      <c r="DB40" s="4"/>
     </row>
     <row r="41" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A41" s="3" t="s">
@@ -5889,12 +5920,14 @@
       <c r="CY41" s="4"/>
       <c r="CZ41" s="4"/>
       <c r="DA41" s="4"/>
+      <c r="DB41" s="4"/>
     </row>
     <row r="42" spans="1:179" x14ac:dyDescent="0.2">
       <c r="CX42" s="4"/>
       <c r="CY42" s="4"/>
       <c r="CZ42" s="4"/>
       <c r="DA42" s="4"/>
+      <c r="DB42" s="4"/>
     </row>
     <row r="43" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A43" s="3" t="s">
@@ -5908,6 +5941,7 @@
       <c r="CY43" s="4"/>
       <c r="CZ43" s="4"/>
       <c r="DA43" s="4"/>
+      <c r="DB43" s="4"/>
     </row>
     <row r="44" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A44" s="1" t="s">
@@ -5921,6 +5955,7 @@
       <c r="CY44" s="4"/>
       <c r="CZ44" s="4"/>
       <c r="DA44" s="4"/>
+      <c r="DB44" s="4"/>
     </row>
     <row r="45" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A45" s="3" t="s">
@@ -5932,12 +5967,14 @@
       <c r="CY45" s="4"/>
       <c r="CZ45" s="4"/>
       <c r="DA45" s="4"/>
+      <c r="DB45" s="4"/>
     </row>
     <row r="46" spans="1:179" x14ac:dyDescent="0.2">
       <c r="CX46" s="4"/>
       <c r="CY46" s="4"/>
       <c r="CZ46" s="4"/>
       <c r="DA46" s="4"/>
+      <c r="DB46" s="4"/>
     </row>
     <row r="47" spans="1:179" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A47" s="16"/>
@@ -6091,10 +6128,13 @@
       <c r="CU47" s="20"/>
       <c r="CV47" s="20"/>
       <c r="CW47" s="20"/>
-      <c r="CX47" s="21"/>
+      <c r="CX47" s="20" t="s">
+        <v>53</v>
+      </c>
       <c r="CY47" s="21"/>
       <c r="CZ47" s="21"/>
       <c r="DA47" s="21"/>
+      <c r="DB47" s="21"/>
     </row>
     <row r="48" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A48" s="5" t="s">
@@ -6400,17 +6440,20 @@
       <c r="CW48" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="CX48" s="22"/>
+      <c r="CX48" s="5" t="s">
+        <v>2</v>
+      </c>
       <c r="CY48" s="22"/>
       <c r="CZ48" s="22"/>
       <c r="DA48" s="22"/>
+      <c r="DB48" s="22"/>
     </row>
     <row r="49" spans="1:175" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="6"/>
-      <c r="CX49" s="4"/>
       <c r="CY49" s="4"/>
       <c r="CZ49" s="4"/>
       <c r="DA49" s="4"/>
+      <c r="DB49" s="4"/>
     </row>
     <row r="50" spans="1:175" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="3" t="s">
@@ -6716,11 +6759,13 @@
       <c r="CW50" s="15">
         <v>7.5731080501705321</v>
       </c>
-      <c r="CX50" s="17"/>
+      <c r="CX50" s="15">
+        <v>8.0623991227815566</v>
+      </c>
       <c r="CY50" s="17"/>
       <c r="CZ50" s="17"/>
       <c r="DA50" s="17"/>
-      <c r="DB50" s="8"/>
+      <c r="DB50" s="17"/>
       <c r="DC50" s="8"/>
       <c r="DD50" s="8"/>
       <c r="DE50" s="8"/>
@@ -7095,11 +7140,13 @@
       <c r="CW51" s="15">
         <v>4.8402265793404666</v>
       </c>
-      <c r="CX51" s="17"/>
+      <c r="CX51" s="15">
+        <v>5.4583195110543841</v>
+      </c>
       <c r="CY51" s="17"/>
       <c r="CZ51" s="17"/>
       <c r="DA51" s="17"/>
-      <c r="DB51" s="8"/>
+      <c r="DB51" s="17"/>
       <c r="DC51" s="8"/>
       <c r="DD51" s="8"/>
       <c r="DE51" s="8"/>
@@ -7272,11 +7319,11 @@
       <c r="CU52" s="8"/>
       <c r="CV52" s="8"/>
       <c r="CW52" s="8"/>
-      <c r="CX52" s="7"/>
+      <c r="CX52" s="8"/>
       <c r="CY52" s="7"/>
       <c r="CZ52" s="7"/>
       <c r="DA52" s="7"/>
-      <c r="DB52" s="8"/>
+      <c r="DB52" s="7"/>
       <c r="DC52" s="8"/>
       <c r="DD52" s="8"/>
       <c r="DE52" s="8"/>
@@ -7651,11 +7698,13 @@
       <c r="CW53" s="15">
         <v>6.3111990197272974</v>
       </c>
-      <c r="CX53" s="17"/>
+      <c r="CX53" s="15">
+        <v>6.8038446698033539</v>
+      </c>
       <c r="CY53" s="17"/>
       <c r="CZ53" s="17"/>
       <c r="DA53" s="17"/>
-      <c r="DB53" s="8"/>
+      <c r="DB53" s="17"/>
       <c r="DC53" s="8"/>
       <c r="DD53" s="8"/>
       <c r="DE53" s="8"/>
@@ -7828,19 +7877,20 @@
       <c r="CU54" s="10"/>
       <c r="CV54" s="10"/>
       <c r="CW54" s="10"/>
-      <c r="CX54" s="23"/>
+      <c r="CX54" s="10"/>
       <c r="CY54" s="23"/>
       <c r="CZ54" s="23"/>
       <c r="DA54" s="23"/>
+      <c r="DB54" s="23"/>
     </row>
     <row r="55" spans="1:175" x14ac:dyDescent="0.2">
       <c r="A55" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="CX55" s="4"/>
       <c r="CY55" s="4"/>
       <c r="CZ55" s="4"/>
       <c r="DA55" s="4"/>
+      <c r="DB55" s="4"/>
     </row>
     <row r="56" spans="1:175" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B56" s="8"/>
@@ -7943,11 +7993,11 @@
       <c r="CU56" s="8"/>
       <c r="CV56" s="8"/>
       <c r="CW56" s="8"/>
-      <c r="CX56" s="7"/>
+      <c r="CX56" s="8"/>
       <c r="CY56" s="7"/>
       <c r="CZ56" s="7"/>
       <c r="DA56" s="7"/>
-      <c r="DB56" s="8"/>
+      <c r="DB56" s="7"/>
       <c r="DC56" s="8"/>
       <c r="DD56" s="8"/>
       <c r="DE56" s="8"/>
@@ -8119,11 +8169,11 @@
       <c r="CU57" s="8"/>
       <c r="CV57" s="8"/>
       <c r="CW57" s="8"/>
-      <c r="CX57" s="7"/>
+      <c r="CX57" s="8"/>
       <c r="CY57" s="7"/>
       <c r="CZ57" s="7"/>
       <c r="DA57" s="7"/>
-      <c r="DB57" s="8"/>
+      <c r="DB57" s="7"/>
       <c r="DC57" s="8"/>
       <c r="DD57" s="8"/>
       <c r="DE57" s="8"/>
@@ -8198,67 +8248,67 @@
       <c r="A58" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="CX58" s="4"/>
       <c r="CY58" s="4"/>
       <c r="CZ58" s="4"/>
       <c r="DA58" s="4"/>
+      <c r="DB58" s="4"/>
     </row>
     <row r="59" spans="1:175" x14ac:dyDescent="0.2">
       <c r="A59" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="CX59" s="4"/>
       <c r="CY59" s="4"/>
       <c r="CZ59" s="4"/>
       <c r="DA59" s="4"/>
+      <c r="DB59" s="4"/>
     </row>
     <row r="60" spans="1:175" x14ac:dyDescent="0.2">
       <c r="A60" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="CX60" s="4"/>
       <c r="CY60" s="4"/>
       <c r="CZ60" s="4"/>
       <c r="DA60" s="4"/>
+      <c r="DB60" s="4"/>
     </row>
     <row r="61" spans="1:175" x14ac:dyDescent="0.2">
-      <c r="CX61" s="4"/>
       <c r="CY61" s="4"/>
       <c r="CZ61" s="4"/>
       <c r="DA61" s="4"/>
+      <c r="DB61" s="4"/>
     </row>
     <row r="62" spans="1:175" x14ac:dyDescent="0.2">
       <c r="A62" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="CX62" s="4"/>
       <c r="CY62" s="4"/>
       <c r="CZ62" s="4"/>
       <c r="DA62" s="4"/>
+      <c r="DB62" s="4"/>
     </row>
     <row r="63" spans="1:175" x14ac:dyDescent="0.2">
       <c r="A63" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="CX63" s="4"/>
       <c r="CY63" s="4"/>
       <c r="CZ63" s="4"/>
       <c r="DA63" s="4"/>
+      <c r="DB63" s="4"/>
     </row>
     <row r="64" spans="1:175" x14ac:dyDescent="0.2">
       <c r="A64" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="CX64" s="4"/>
       <c r="CY64" s="4"/>
       <c r="CZ64" s="4"/>
       <c r="DA64" s="4"/>
+      <c r="DB64" s="4"/>
     </row>
     <row r="65" spans="1:179" x14ac:dyDescent="0.2">
-      <c r="CX65" s="4"/>
       <c r="CY65" s="4"/>
       <c r="CZ65" s="4"/>
       <c r="DA65" s="4"/>
+      <c r="DB65" s="4"/>
     </row>
     <row r="66" spans="1:179" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A66" s="16"/>
@@ -8412,10 +8462,13 @@
       <c r="CU66" s="20"/>
       <c r="CV66" s="20"/>
       <c r="CW66" s="20"/>
-      <c r="CX66" s="21"/>
+      <c r="CX66" s="20" t="s">
+        <v>53</v>
+      </c>
       <c r="CY66" s="21"/>
       <c r="CZ66" s="21"/>
       <c r="DA66" s="21"/>
+      <c r="DB66" s="21"/>
     </row>
     <row r="67" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A67" s="5" t="s">
@@ -8721,17 +8774,20 @@
       <c r="CW67" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="CX67" s="22"/>
+      <c r="CX67" s="5" t="s">
+        <v>2</v>
+      </c>
       <c r="CY67" s="22"/>
       <c r="CZ67" s="22"/>
       <c r="DA67" s="22"/>
+      <c r="DB67" s="22"/>
     </row>
     <row r="68" spans="1:179" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A68" s="6"/>
-      <c r="CX68" s="4"/>
       <c r="CY68" s="4"/>
       <c r="CZ68" s="4"/>
       <c r="DA68" s="4"/>
+      <c r="DB68" s="4"/>
     </row>
     <row r="69" spans="1:179" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A69" s="3" t="s">
@@ -9037,11 +9093,13 @@
       <c r="CW69" s="15">
         <v>6.2520349173921232</v>
       </c>
-      <c r="CX69" s="17"/>
+      <c r="CX69" s="15">
+        <v>4.9734298148619303</v>
+      </c>
       <c r="CY69" s="17"/>
       <c r="CZ69" s="17"/>
       <c r="DA69" s="17"/>
-      <c r="DB69" s="8"/>
+      <c r="DB69" s="17"/>
       <c r="DC69" s="8"/>
       <c r="DD69" s="8"/>
       <c r="DE69" s="8"/>
@@ -9416,11 +9474,13 @@
       <c r="CW70" s="15">
         <v>2.289014546709339</v>
       </c>
-      <c r="CX70" s="17"/>
+      <c r="CX70" s="15">
+        <v>1.6975933887658101</v>
+      </c>
       <c r="CY70" s="17"/>
       <c r="CZ70" s="17"/>
       <c r="DA70" s="17"/>
-      <c r="DB70" s="8"/>
+      <c r="DB70" s="17"/>
       <c r="DC70" s="8"/>
       <c r="DD70" s="8"/>
       <c r="DE70" s="8"/>
@@ -9592,11 +9652,11 @@
       <c r="CU71" s="8"/>
       <c r="CV71" s="8"/>
       <c r="CW71" s="8"/>
-      <c r="CX71" s="7"/>
+      <c r="CX71" s="8"/>
       <c r="CY71" s="7"/>
       <c r="CZ71" s="7"/>
       <c r="DA71" s="7"/>
-      <c r="DB71" s="8"/>
+      <c r="DB71" s="7"/>
       <c r="DC71" s="8"/>
       <c r="DD71" s="8"/>
       <c r="DE71" s="8"/>
@@ -9971,11 +10031,13 @@
       <c r="CW72" s="15">
         <v>4.3443836361580139</v>
       </c>
-      <c r="CX72" s="17"/>
+      <c r="CX72" s="15">
+        <v>3.3080120949772578</v>
+      </c>
       <c r="CY72" s="17"/>
       <c r="CZ72" s="17"/>
       <c r="DA72" s="17"/>
-      <c r="DB72" s="8"/>
+      <c r="DB72" s="17"/>
       <c r="DC72" s="8"/>
       <c r="DD72" s="8"/>
       <c r="DE72" s="8"/>
@@ -10148,19 +10210,20 @@
       <c r="CU73" s="10"/>
       <c r="CV73" s="10"/>
       <c r="CW73" s="10"/>
-      <c r="CX73" s="23"/>
+      <c r="CX73" s="10"/>
       <c r="CY73" s="23"/>
       <c r="CZ73" s="23"/>
       <c r="DA73" s="23"/>
+      <c r="DB73" s="23"/>
     </row>
     <row r="74" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A74" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="CX74" s="4"/>
       <c r="CY74" s="4"/>
       <c r="CZ74" s="4"/>
       <c r="DA74" s="4"/>
+      <c r="DB74" s="4"/>
     </row>
     <row r="75" spans="1:179" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B75" s="8"/>
@@ -10267,7 +10330,7 @@
       <c r="CY75" s="7"/>
       <c r="CZ75" s="7"/>
       <c r="DA75" s="7"/>
-      <c r="DB75" s="8"/>
+      <c r="DB75" s="7"/>
       <c r="DC75" s="8"/>
       <c r="DD75" s="8"/>
       <c r="DE75" s="8"/>
@@ -10443,7 +10506,7 @@
       <c r="CY76" s="7"/>
       <c r="CZ76" s="7"/>
       <c r="DA76" s="7"/>
-      <c r="DB76" s="8"/>
+      <c r="DB76" s="7"/>
       <c r="DC76" s="8"/>
       <c r="DD76" s="8"/>
       <c r="DE76" s="8"/>
@@ -10526,6 +10589,7 @@
       <c r="CY77" s="4"/>
       <c r="CZ77" s="4"/>
       <c r="DA77" s="4"/>
+      <c r="DB77" s="4"/>
     </row>
     <row r="78" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A78" s="3" t="s">
@@ -10535,12 +10599,14 @@
       <c r="CY78" s="4"/>
       <c r="CZ78" s="4"/>
       <c r="DA78" s="4"/>
+      <c r="DB78" s="4"/>
     </row>
     <row r="79" spans="1:179" x14ac:dyDescent="0.2">
       <c r="CX79" s="4"/>
       <c r="CY79" s="4"/>
       <c r="CZ79" s="4"/>
       <c r="DA79" s="4"/>
+      <c r="DB79" s="4"/>
     </row>
     <row r="80" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A80" s="3" t="s">
@@ -10550,6 +10616,7 @@
       <c r="CY80" s="4"/>
       <c r="CZ80" s="4"/>
       <c r="DA80" s="4"/>
+      <c r="DB80" s="4"/>
     </row>
     <row r="81" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A81" s="3" t="s">
@@ -10559,6 +10626,7 @@
       <c r="CY81" s="4"/>
       <c r="CZ81" s="4"/>
       <c r="DA81" s="4"/>
+      <c r="DB81" s="4"/>
     </row>
     <row r="82" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A82" s="3" t="s">
@@ -10568,6 +10636,7 @@
       <c r="CY82" s="4"/>
       <c r="CZ82" s="4"/>
       <c r="DA82" s="4"/>
+      <c r="DB82" s="4"/>
     </row>
     <row r="84" spans="1:179" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A84" s="16"/>
@@ -10727,6 +10796,9 @@
       <c r="CY84" s="20"/>
       <c r="CZ84" s="20"/>
       <c r="DA84" s="20"/>
+      <c r="DB84" s="20">
+        <v>2026</v>
+      </c>
     </row>
     <row r="85" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A85" s="5" t="s">
@@ -11043,6 +11115,9 @@
       </c>
       <c r="DA85" s="12" t="s">
         <v>5</v>
+      </c>
+      <c r="DB85" s="12" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="86" spans="1:179" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
@@ -11364,7 +11439,9 @@
       <c r="DA87" s="15">
         <v>130.31635891990027</v>
       </c>
-      <c r="DB87" s="8"/>
+      <c r="DB87" s="15">
+        <v>135.64244603508024</v>
+      </c>
       <c r="DC87" s="8"/>
       <c r="DD87" s="8"/>
       <c r="DE87" s="8"/>
@@ -11755,7 +11832,9 @@
       <c r="DA88" s="15">
         <v>121.93988402904634</v>
       </c>
-      <c r="DB88" s="8"/>
+      <c r="DB88" s="15">
+        <v>123.58517557586259</v>
+      </c>
       <c r="DC88" s="8"/>
       <c r="DD88" s="8"/>
       <c r="DE88" s="8"/>
@@ -12326,7 +12405,9 @@
       <c r="DA90" s="15">
         <v>126.36365857630096</v>
       </c>
-      <c r="DB90" s="8"/>
+      <c r="DB90" s="15">
+        <v>129.60814951528002</v>
+      </c>
       <c r="DC90" s="8"/>
       <c r="DD90" s="8"/>
       <c r="DE90" s="8"/>
@@ -12507,6 +12588,7 @@
       <c r="CY91" s="10"/>
       <c r="CZ91" s="10"/>
       <c r="DA91" s="10"/>
+      <c r="DB91" s="10"/>
     </row>
     <row r="92" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A92" s="11" t="s">
@@ -12701,6 +12783,9 @@
       <c r="CY103" s="20"/>
       <c r="CZ103" s="20"/>
       <c r="DA103" s="20"/>
+      <c r="DB103" s="20">
+        <v>2026</v>
+      </c>
     </row>
     <row r="104" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A104" s="5" t="s">
@@ -13017,6 +13102,9 @@
       </c>
       <c r="DA104" s="12" t="s">
         <v>5</v>
+      </c>
+      <c r="DB104" s="12" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="105" spans="1:179" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
@@ -13338,7 +13426,9 @@
       <c r="DA106" s="15">
         <v>54.463862824494647</v>
       </c>
-      <c r="DB106" s="8"/>
+      <c r="DB106" s="15">
+        <v>52.278760728663606</v>
+      </c>
       <c r="DC106" s="8"/>
       <c r="DD106" s="8"/>
       <c r="DE106" s="8"/>
@@ -13729,7 +13819,9 @@
       <c r="DA107" s="15">
         <v>45.536137175505367</v>
       </c>
-      <c r="DB107" s="8"/>
+      <c r="DB107" s="15">
+        <v>47.721239271336394</v>
+      </c>
       <c r="DC107" s="8"/>
       <c r="DD107" s="8"/>
       <c r="DE107" s="8"/>
@@ -14300,7 +14392,9 @@
       <c r="DA109" s="15">
         <v>100</v>
       </c>
-      <c r="DB109" s="8"/>
+      <c r="DB109" s="15">
+        <v>100</v>
+      </c>
       <c r="DC109" s="8"/>
       <c r="DD109" s="8"/>
       <c r="DE109" s="8"/>
@@ -14481,6 +14575,7 @@
       <c r="CY110" s="10"/>
       <c r="CZ110" s="10"/>
       <c r="DA110" s="10"/>
+      <c r="DB110" s="10"/>
     </row>
     <row r="111" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A111" s="11" t="s">
@@ -15035,6 +15130,9 @@
       <c r="CY122" s="20"/>
       <c r="CZ122" s="20"/>
       <c r="DA122" s="20"/>
+      <c r="DB122" s="20">
+        <v>2026</v>
+      </c>
     </row>
     <row r="123" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A123" s="5" t="s">
@@ -15351,6 +15449,9 @@
       </c>
       <c r="DA123" s="12" t="s">
         <v>5</v>
+      </c>
+      <c r="DB123" s="12" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="124" spans="1:179" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
@@ -15672,7 +15773,9 @@
       <c r="DA125" s="15">
         <v>52.811888113994577</v>
       </c>
-      <c r="DB125" s="8"/>
+      <c r="DB125" s="15">
+        <v>49.953046668310733</v>
+      </c>
       <c r="DC125" s="8"/>
       <c r="DD125" s="8"/>
       <c r="DE125" s="8"/>
@@ -16063,7 +16166,9 @@
       <c r="DA126" s="15">
         <v>47.18811188600543</v>
       </c>
-      <c r="DB126" s="8"/>
+      <c r="DB126" s="15">
+        <v>50.046953331689267</v>
+      </c>
       <c r="DC126" s="8"/>
       <c r="DD126" s="8"/>
       <c r="DE126" s="8"/>
@@ -16634,7 +16739,9 @@
       <c r="DA128" s="15">
         <v>100</v>
       </c>
-      <c r="DB128" s="8"/>
+      <c r="DB128" s="15">
+        <v>100</v>
+      </c>
       <c r="DC128" s="8"/>
       <c r="DD128" s="8"/>
       <c r="DE128" s="8"/>
@@ -16815,6 +16922,7 @@
       <c r="CY129" s="10"/>
       <c r="CZ129" s="10"/>
       <c r="DA129" s="10"/>
+      <c r="DB129" s="10"/>
     </row>
     <row r="130" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A130" s="11" t="s">
@@ -16927,7 +17035,7 @@
       <c r="CY131" s="24"/>
       <c r="CZ131" s="24"/>
       <c r="DA131" s="24"/>
-      <c r="DB131" s="13"/>
+      <c r="DB131" s="24"/>
       <c r="DC131" s="13"/>
       <c r="DD131" s="13"/>
       <c r="DE131" s="13"/>
@@ -17007,6 +17115,7 @@
       <c r="CY132" s="4"/>
       <c r="CZ132" s="4"/>
       <c r="DA132" s="4"/>
+      <c r="DB132" s="6"/>
     </row>
     <row r="133" spans="1:179" x14ac:dyDescent="0.2">
       <c r="CT133" s="6"/>
@@ -17016,6 +17125,7 @@
       <c r="CY133" s="6"/>
       <c r="CZ133" s="6"/>
       <c r="DA133" s="6"/>
+      <c r="DB133" s="6"/>
     </row>
     <row r="134" spans="1:179" x14ac:dyDescent="0.2">
       <c r="CT134" s="6"/>
@@ -17041,9 +17151,9 @@
   <pageSetup paperSize="9" scale="48" orientation="landscape" r:id="rId1"/>
   <headerFooter alignWithMargins="0"/>
   <rowBreaks count="3" manualBreakCount="3">
-    <brk id="38" max="81" man="1"/>
-    <brk id="76" max="189" man="1"/>
-    <brk id="94" max="81" man="1"/>
+    <brk id="38" max="105" man="1"/>
+    <brk id="76" max="105" man="1"/>
+    <brk id="94" max="105" man="1"/>
   </rowBreaks>
 </worksheet>
 </file>
--- a/Data/National Accounts/PSA-18REOD_2018PSNA_Qrt.xlsx
+++ b/Data/National Accounts/PSA-18REOD_2018PSNA_Qrt.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\Shared drives\QNAP\NAP Dissemination\As of May 2026\Tables\NAP Q1 2000 to Q1 2026\Qtr\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\Shared drives\QNAP\NAP Dissemination\As of August 2026\Tables\NAP Q1 2000 to Q2 2026\Qtr\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C7A8A01-8E71-485D-83FD-C55BD26AEF9D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F102556-9AB3-4663-9DCA-0B4280ADE542}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="794" xr2:uid="{736930C2-BFBB-46C3-AE9E-AECFC8C3145D}"/>
   </bookViews>
@@ -356,7 +356,7 @@
     <definedName name="pet">#REF!</definedName>
     <definedName name="plastic">#REF!</definedName>
     <definedName name="ply">#REF!</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">REOD!$A$1:$DB$131</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">REOD!$A$1:$DC$131</definedName>
     <definedName name="_xlnm.Print_Area">#REF!</definedName>
     <definedName name="PRINT_AREA_MI">#REF!</definedName>
     <definedName name="Print_Titles_MI">#REF!,#REF!</definedName>
@@ -530,7 +530,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="855" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="862" uniqueCount="54">
   <si>
     <t>National Accounts of the Philippines</t>
   </si>
@@ -685,13 +685,13 @@
     <t>Table 19.7 Gross Value Added in Real Estate and Ownership of Dwellings , by Industry</t>
   </si>
   <si>
-    <t>Q1 2000 to Q1 2026</t>
+    <t>2025 - 2026</t>
   </si>
   <si>
-    <t>As of May 2026</t>
+    <t>Q1 2000 to Q2 2026</t>
   </si>
   <si>
-    <t>2025 - 2026</t>
+    <t>As of August 2026</t>
   </si>
 </sst>
 </file>
@@ -1194,8 +1194,8 @@
   <sheetFormatPr defaultColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="49.28515625" style="3" customWidth="1"/>
-    <col min="2" max="106" width="13" style="3" customWidth="1"/>
-    <col min="107" max="16384" width="10" style="3"/>
+    <col min="2" max="107" width="13" style="3" customWidth="1"/>
+    <col min="108" max="16384" width="10" style="3"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:179" x14ac:dyDescent="0.2">
@@ -1210,7 +1210,7 @@
     </row>
     <row r="3" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="5" spans="1:179" x14ac:dyDescent="0.2">
@@ -1220,7 +1220,7 @@
     </row>
     <row r="6" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="7" spans="1:179" x14ac:dyDescent="0.2">
@@ -1389,6 +1389,7 @@
       <c r="DB9" s="20">
         <v>2026</v>
       </c>
+      <c r="DC9" s="20"/>
     </row>
     <row r="10" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A10" s="5" t="s">
@@ -1708,6 +1709,9 @@
       </c>
       <c r="DB10" s="12" t="s">
         <v>2</v>
+      </c>
+      <c r="DC10" s="12" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="11" spans="1:179" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
@@ -2030,9 +2034,11 @@
         <v>221017.2832523628</v>
       </c>
       <c r="DB12" s="18">
-        <v>209954.43739119213</v>
-      </c>
-      <c r="DC12" s="8"/>
+        <v>209325.29053668887</v>
+      </c>
+      <c r="DC12" s="18">
+        <v>227379.33504831581</v>
+      </c>
       <c r="DD12" s="8"/>
       <c r="DE12" s="8"/>
       <c r="DF12" s="8"/>
@@ -2423,9 +2429,11 @@
         <v>184788.09262516719</v>
       </c>
       <c r="DB13" s="18">
-        <v>191651.17541377526</v>
-      </c>
-      <c r="DC13" s="8"/>
+        <v>191655.3808871232</v>
+      </c>
+      <c r="DC13" s="18">
+        <v>194979.78836613419</v>
+      </c>
       <c r="DD13" s="8"/>
       <c r="DE13" s="8"/>
       <c r="DF13" s="8"/>
@@ -2996,9 +3004,11 @@
         <v>405805.37587752996</v>
       </c>
       <c r="DB15" s="19">
-        <v>401605.61280496739</v>
-      </c>
-      <c r="DC15" s="8"/>
+        <v>400980.67142381205</v>
+      </c>
+      <c r="DC15" s="19">
+        <v>422359.12341444998</v>
+      </c>
       <c r="DD15" s="8"/>
       <c r="DE15" s="8"/>
       <c r="DF15" s="8"/>
@@ -3179,6 +3189,7 @@
       <c r="CZ16" s="10"/>
       <c r="DA16" s="10"/>
       <c r="DB16" s="10"/>
+      <c r="DC16" s="10"/>
     </row>
     <row r="17" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A17" s="11" t="s">
@@ -3557,7 +3568,7 @@
     </row>
     <row r="22" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A22" s="3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="24" spans="1:179" x14ac:dyDescent="0.2">
@@ -3567,7 +3578,7 @@
     </row>
     <row r="25" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A25" s="3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="26" spans="1:179" x14ac:dyDescent="0.2">
@@ -3736,6 +3747,7 @@
       <c r="DB28" s="20">
         <v>2026</v>
       </c>
+      <c r="DC28" s="20"/>
     </row>
     <row r="29" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A29" s="5" t="s">
@@ -4055,6 +4067,9 @@
       </c>
       <c r="DB29" s="12" t="s">
         <v>2</v>
+      </c>
+      <c r="DC29" s="12" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="30" spans="1:179" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
@@ -4377,9 +4392,11 @@
         <v>169600.56671642614</v>
       </c>
       <c r="DB31" s="18">
-        <v>154785.20443143079</v>
-      </c>
-      <c r="DC31" s="8"/>
+        <v>154321.3770139124</v>
+      </c>
+      <c r="DC31" s="18">
+        <v>165328.12593891891</v>
+      </c>
       <c r="DD31" s="8"/>
       <c r="DE31" s="8"/>
       <c r="DF31" s="8"/>
@@ -4770,9 +4787,11 @@
         <v>151540.32177130025</v>
       </c>
       <c r="DB32" s="18">
-        <v>155076.18492327217</v>
-      </c>
-      <c r="DC32" s="8"/>
+        <v>155079.83444252735</v>
+      </c>
+      <c r="DC32" s="18">
+        <v>156289.93789967545</v>
+      </c>
       <c r="DD32" s="8"/>
       <c r="DE32" s="8"/>
       <c r="DF32" s="8"/>
@@ -5343,9 +5362,11 @@
         <v>321140.88848772639</v>
       </c>
       <c r="DB34" s="19">
-        <v>309861.38935470296</v>
-      </c>
-      <c r="DC34" s="8"/>
+        <v>309401.21145643975</v>
+      </c>
+      <c r="DC34" s="19">
+        <v>321618.06383859436</v>
+      </c>
       <c r="DD34" s="8"/>
       <c r="DE34" s="8"/>
       <c r="DF34" s="8"/>
@@ -5526,6 +5547,7 @@
       <c r="CZ35" s="10"/>
       <c r="DA35" s="10"/>
       <c r="DB35" s="10"/>
+      <c r="DC35" s="10"/>
     </row>
     <row r="36" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A36" s="11" t="s">
@@ -5638,7 +5660,7 @@
       <c r="CZ37" s="7"/>
       <c r="DA37" s="7"/>
       <c r="DB37" s="7"/>
-      <c r="DC37" s="8"/>
+      <c r="DC37" s="7"/>
       <c r="DD37" s="8"/>
       <c r="DE37" s="8"/>
       <c r="DF37" s="8"/>
@@ -5818,7 +5840,7 @@
       <c r="CZ38" s="7"/>
       <c r="DA38" s="7"/>
       <c r="DB38" s="7"/>
-      <c r="DC38" s="8"/>
+      <c r="DC38" s="7"/>
       <c r="DD38" s="8"/>
       <c r="DE38" s="8"/>
       <c r="DF38" s="8"/>
@@ -5901,6 +5923,7 @@
       <c r="CZ39" s="4"/>
       <c r="DA39" s="4"/>
       <c r="DB39" s="4"/>
+      <c r="DC39" s="4"/>
     </row>
     <row r="40" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A40" s="3" t="s">
@@ -5911,16 +5934,18 @@
       <c r="CZ40" s="4"/>
       <c r="DA40" s="4"/>
       <c r="DB40" s="4"/>
+      <c r="DC40" s="4"/>
     </row>
     <row r="41" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A41" s="3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="CX41" s="4"/>
       <c r="CY41" s="4"/>
       <c r="CZ41" s="4"/>
       <c r="DA41" s="4"/>
       <c r="DB41" s="4"/>
+      <c r="DC41" s="4"/>
     </row>
     <row r="42" spans="1:179" x14ac:dyDescent="0.2">
       <c r="CX42" s="4"/>
@@ -5928,6 +5953,7 @@
       <c r="CZ42" s="4"/>
       <c r="DA42" s="4"/>
       <c r="DB42" s="4"/>
+      <c r="DC42" s="4"/>
     </row>
     <row r="43" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A43" s="3" t="s">
@@ -5942,10 +5968,11 @@
       <c r="CZ43" s="4"/>
       <c r="DA43" s="4"/>
       <c r="DB43" s="4"/>
+      <c r="DC43" s="4"/>
     </row>
     <row r="44" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A44" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="CS44" s="6"/>
       <c r="CT44" s="6"/>
@@ -5956,6 +5983,7 @@
       <c r="CZ44" s="4"/>
       <c r="DA44" s="4"/>
       <c r="DB44" s="4"/>
+      <c r="DC44" s="4"/>
     </row>
     <row r="45" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A45" s="3" t="s">
@@ -5968,13 +5996,13 @@
       <c r="CZ45" s="4"/>
       <c r="DA45" s="4"/>
       <c r="DB45" s="4"/>
+      <c r="DC45" s="4"/>
     </row>
     <row r="46" spans="1:179" x14ac:dyDescent="0.2">
-      <c r="CX46" s="4"/>
-      <c r="CY46" s="4"/>
       <c r="CZ46" s="4"/>
       <c r="DA46" s="4"/>
       <c r="DB46" s="4"/>
+      <c r="DC46" s="4"/>
     </row>
     <row r="47" spans="1:179" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A47" s="16"/>
@@ -6129,12 +6157,13 @@
       <c r="CV47" s="20"/>
       <c r="CW47" s="20"/>
       <c r="CX47" s="20" t="s">
-        <v>53</v>
-      </c>
-      <c r="CY47" s="21"/>
+        <v>51</v>
+      </c>
+      <c r="CY47" s="20"/>
       <c r="CZ47" s="21"/>
       <c r="DA47" s="21"/>
       <c r="DB47" s="21"/>
+      <c r="DC47" s="21"/>
     </row>
     <row r="48" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A48" s="5" t="s">
@@ -6443,17 +6472,20 @@
       <c r="CX48" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="CY48" s="22"/>
+      <c r="CY48" s="5" t="s">
+        <v>3</v>
+      </c>
       <c r="CZ48" s="22"/>
       <c r="DA48" s="22"/>
       <c r="DB48" s="22"/>
+      <c r="DC48" s="22"/>
     </row>
     <row r="49" spans="1:175" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="6"/>
-      <c r="CY49" s="4"/>
       <c r="CZ49" s="4"/>
       <c r="DA49" s="4"/>
       <c r="DB49" s="4"/>
+      <c r="DC49" s="4"/>
     </row>
     <row r="50" spans="1:175" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="3" t="s">
@@ -6760,13 +6792,15 @@
         <v>7.5731080501705321</v>
       </c>
       <c r="CX50" s="15">
-        <v>8.0623991227815566</v>
-      </c>
-      <c r="CY50" s="17"/>
+        <v>7.7385806822524899</v>
+      </c>
+      <c r="CY50" s="15">
+        <v>7.9136187830212776</v>
+      </c>
       <c r="CZ50" s="17"/>
       <c r="DA50" s="17"/>
       <c r="DB50" s="17"/>
-      <c r="DC50" s="8"/>
+      <c r="DC50" s="17"/>
       <c r="DD50" s="8"/>
       <c r="DE50" s="8"/>
       <c r="DF50" s="8"/>
@@ -7141,13 +7175,15 @@
         <v>4.8402265793404666</v>
       </c>
       <c r="CX51" s="15">
-        <v>5.4583195110543841</v>
-      </c>
-      <c r="CY51" s="17"/>
+        <v>5.4606336223613567</v>
+      </c>
+      <c r="CY51" s="15">
+        <v>5.8495987516015333</v>
+      </c>
       <c r="CZ51" s="17"/>
       <c r="DA51" s="17"/>
       <c r="DB51" s="17"/>
-      <c r="DC51" s="8"/>
+      <c r="DC51" s="17"/>
       <c r="DD51" s="8"/>
       <c r="DE51" s="8"/>
       <c r="DF51" s="8"/>
@@ -7320,11 +7356,11 @@
       <c r="CV52" s="8"/>
       <c r="CW52" s="8"/>
       <c r="CX52" s="8"/>
-      <c r="CY52" s="7"/>
+      <c r="CY52" s="8"/>
       <c r="CZ52" s="7"/>
       <c r="DA52" s="7"/>
       <c r="DB52" s="7"/>
-      <c r="DC52" s="8"/>
+      <c r="DC52" s="7"/>
       <c r="DD52" s="8"/>
       <c r="DE52" s="8"/>
       <c r="DF52" s="8"/>
@@ -7699,13 +7735,15 @@
         <v>6.3111990197272974</v>
       </c>
       <c r="CX53" s="15">
-        <v>6.8038446698033539</v>
-      </c>
-      <c r="CY53" s="17"/>
+        <v>6.6376464393192975</v>
+      </c>
+      <c r="CY53" s="15">
+        <v>6.9508617611222974</v>
+      </c>
       <c r="CZ53" s="17"/>
       <c r="DA53" s="17"/>
       <c r="DB53" s="17"/>
-      <c r="DC53" s="8"/>
+      <c r="DC53" s="17"/>
       <c r="DD53" s="8"/>
       <c r="DE53" s="8"/>
       <c r="DF53" s="8"/>
@@ -7878,19 +7916,20 @@
       <c r="CV54" s="10"/>
       <c r="CW54" s="10"/>
       <c r="CX54" s="10"/>
-      <c r="CY54" s="23"/>
+      <c r="CY54" s="10"/>
       <c r="CZ54" s="23"/>
       <c r="DA54" s="23"/>
       <c r="DB54" s="23"/>
+      <c r="DC54" s="23"/>
     </row>
     <row r="55" spans="1:175" x14ac:dyDescent="0.2">
       <c r="A55" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="CY55" s="4"/>
       <c r="CZ55" s="4"/>
       <c r="DA55" s="4"/>
       <c r="DB55" s="4"/>
+      <c r="DC55" s="4"/>
     </row>
     <row r="56" spans="1:175" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B56" s="8"/>
@@ -7994,11 +8033,11 @@
       <c r="CV56" s="8"/>
       <c r="CW56" s="8"/>
       <c r="CX56" s="8"/>
-      <c r="CY56" s="7"/>
+      <c r="CY56" s="8"/>
       <c r="CZ56" s="7"/>
       <c r="DA56" s="7"/>
       <c r="DB56" s="7"/>
-      <c r="DC56" s="8"/>
+      <c r="DC56" s="7"/>
       <c r="DD56" s="8"/>
       <c r="DE56" s="8"/>
       <c r="DF56" s="8"/>
@@ -8170,11 +8209,11 @@
       <c r="CV57" s="8"/>
       <c r="CW57" s="8"/>
       <c r="CX57" s="8"/>
-      <c r="CY57" s="7"/>
+      <c r="CY57" s="8"/>
       <c r="CZ57" s="7"/>
       <c r="DA57" s="7"/>
       <c r="DB57" s="7"/>
-      <c r="DC57" s="8"/>
+      <c r="DC57" s="7"/>
       <c r="DD57" s="8"/>
       <c r="DE57" s="8"/>
       <c r="DF57" s="8"/>
@@ -8248,67 +8287,67 @@
       <c r="A58" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="CY58" s="4"/>
       <c r="CZ58" s="4"/>
       <c r="DA58" s="4"/>
       <c r="DB58" s="4"/>
+      <c r="DC58" s="4"/>
     </row>
     <row r="59" spans="1:175" x14ac:dyDescent="0.2">
       <c r="A59" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="CY59" s="4"/>
       <c r="CZ59" s="4"/>
       <c r="DA59" s="4"/>
       <c r="DB59" s="4"/>
+      <c r="DC59" s="4"/>
     </row>
     <row r="60" spans="1:175" x14ac:dyDescent="0.2">
       <c r="A60" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="CY60" s="4"/>
+        <v>53</v>
+      </c>
       <c r="CZ60" s="4"/>
       <c r="DA60" s="4"/>
       <c r="DB60" s="4"/>
+      <c r="DC60" s="4"/>
     </row>
     <row r="61" spans="1:175" x14ac:dyDescent="0.2">
-      <c r="CY61" s="4"/>
       <c r="CZ61" s="4"/>
       <c r="DA61" s="4"/>
       <c r="DB61" s="4"/>
+      <c r="DC61" s="4"/>
     </row>
     <row r="62" spans="1:175" x14ac:dyDescent="0.2">
       <c r="A62" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="CY62" s="4"/>
       <c r="CZ62" s="4"/>
       <c r="DA62" s="4"/>
       <c r="DB62" s="4"/>
+      <c r="DC62" s="4"/>
     </row>
     <row r="63" spans="1:175" x14ac:dyDescent="0.2">
       <c r="A63" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="CY63" s="4"/>
+        <v>52</v>
+      </c>
       <c r="CZ63" s="4"/>
       <c r="DA63" s="4"/>
       <c r="DB63" s="4"/>
+      <c r="DC63" s="4"/>
     </row>
     <row r="64" spans="1:175" x14ac:dyDescent="0.2">
       <c r="A64" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="CY64" s="4"/>
       <c r="CZ64" s="4"/>
       <c r="DA64" s="4"/>
       <c r="DB64" s="4"/>
+      <c r="DC64" s="4"/>
     </row>
     <row r="65" spans="1:179" x14ac:dyDescent="0.2">
-      <c r="CY65" s="4"/>
       <c r="CZ65" s="4"/>
       <c r="DA65" s="4"/>
       <c r="DB65" s="4"/>
+      <c r="DC65" s="4"/>
     </row>
     <row r="66" spans="1:179" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A66" s="16"/>
@@ -8463,12 +8502,13 @@
       <c r="CV66" s="20"/>
       <c r="CW66" s="20"/>
       <c r="CX66" s="20" t="s">
-        <v>53</v>
-      </c>
-      <c r="CY66" s="21"/>
+        <v>51</v>
+      </c>
+      <c r="CY66" s="20"/>
       <c r="CZ66" s="21"/>
       <c r="DA66" s="21"/>
       <c r="DB66" s="21"/>
+      <c r="DC66" s="21"/>
     </row>
     <row r="67" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A67" s="5" t="s">
@@ -8777,17 +8817,20 @@
       <c r="CX67" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="CY67" s="22"/>
+      <c r="CY67" s="5" t="s">
+        <v>3</v>
+      </c>
       <c r="CZ67" s="22"/>
       <c r="DA67" s="22"/>
       <c r="DB67" s="22"/>
+      <c r="DC67" s="22"/>
     </row>
     <row r="68" spans="1:179" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A68" s="6"/>
-      <c r="CY68" s="4"/>
       <c r="CZ68" s="4"/>
       <c r="DA68" s="4"/>
       <c r="DB68" s="4"/>
+      <c r="DC68" s="4"/>
     </row>
     <row r="69" spans="1:179" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A69" s="3" t="s">
@@ -9094,13 +9137,15 @@
         <v>6.2520349173921232</v>
       </c>
       <c r="CX69" s="15">
-        <v>4.9734298148619303</v>
-      </c>
-      <c r="CY69" s="17"/>
+        <v>4.6588677413231636</v>
+      </c>
+      <c r="CY69" s="15">
+        <v>0.75817892518385577</v>
+      </c>
       <c r="CZ69" s="17"/>
       <c r="DA69" s="17"/>
       <c r="DB69" s="17"/>
-      <c r="DC69" s="8"/>
+      <c r="DC69" s="17"/>
       <c r="DD69" s="8"/>
       <c r="DE69" s="8"/>
       <c r="DF69" s="8"/>
@@ -9475,13 +9520,15 @@
         <v>2.289014546709339</v>
       </c>
       <c r="CX70" s="15">
-        <v>1.6975933887658101</v>
-      </c>
-      <c r="CY70" s="17"/>
+        <v>1.6999867112831311</v>
+      </c>
+      <c r="CY70" s="15">
+        <v>1.8317845247297129</v>
+      </c>
       <c r="CZ70" s="17"/>
       <c r="DA70" s="17"/>
       <c r="DB70" s="17"/>
-      <c r="DC70" s="8"/>
+      <c r="DC70" s="17"/>
       <c r="DD70" s="8"/>
       <c r="DE70" s="8"/>
       <c r="DF70" s="8"/>
@@ -9653,11 +9700,11 @@
       <c r="CV71" s="8"/>
       <c r="CW71" s="8"/>
       <c r="CX71" s="8"/>
-      <c r="CY71" s="7"/>
+      <c r="CY71" s="8"/>
       <c r="CZ71" s="7"/>
       <c r="DA71" s="7"/>
       <c r="DB71" s="7"/>
-      <c r="DC71" s="8"/>
+      <c r="DC71" s="7"/>
       <c r="DD71" s="8"/>
       <c r="DE71" s="8"/>
       <c r="DF71" s="8"/>
@@ -10032,13 +10079,15 @@
         <v>4.3443836361580139</v>
       </c>
       <c r="CX72" s="15">
-        <v>3.3080120949772578</v>
-      </c>
-      <c r="CY72" s="17"/>
+        <v>3.1545884497189007</v>
+      </c>
+      <c r="CY72" s="15">
+        <v>1.2770542999756032</v>
+      </c>
       <c r="CZ72" s="17"/>
       <c r="DA72" s="17"/>
       <c r="DB72" s="17"/>
-      <c r="DC72" s="8"/>
+      <c r="DC72" s="17"/>
       <c r="DD72" s="8"/>
       <c r="DE72" s="8"/>
       <c r="DF72" s="8"/>
@@ -10211,19 +10260,20 @@
       <c r="CV73" s="10"/>
       <c r="CW73" s="10"/>
       <c r="CX73" s="10"/>
-      <c r="CY73" s="23"/>
+      <c r="CY73" s="10"/>
       <c r="CZ73" s="23"/>
       <c r="DA73" s="23"/>
       <c r="DB73" s="23"/>
+      <c r="DC73" s="23"/>
     </row>
     <row r="74" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A74" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="CY74" s="4"/>
       <c r="CZ74" s="4"/>
       <c r="DA74" s="4"/>
       <c r="DB74" s="4"/>
+      <c r="DC74" s="4"/>
     </row>
     <row r="75" spans="1:179" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B75" s="8"/>
@@ -10327,11 +10377,11 @@
       <c r="CV75" s="8"/>
       <c r="CW75" s="8"/>
       <c r="CX75" s="7"/>
-      <c r="CY75" s="7"/>
+      <c r="CY75" s="8"/>
       <c r="CZ75" s="7"/>
       <c r="DA75" s="7"/>
       <c r="DB75" s="7"/>
-      <c r="DC75" s="8"/>
+      <c r="DC75" s="7"/>
       <c r="DD75" s="8"/>
       <c r="DE75" s="8"/>
       <c r="DF75" s="8"/>
@@ -10507,7 +10557,7 @@
       <c r="CZ76" s="7"/>
       <c r="DA76" s="7"/>
       <c r="DB76" s="7"/>
-      <c r="DC76" s="8"/>
+      <c r="DC76" s="7"/>
       <c r="DD76" s="8"/>
       <c r="DE76" s="8"/>
       <c r="DF76" s="8"/>
@@ -10590,16 +10640,18 @@
       <c r="CZ77" s="4"/>
       <c r="DA77" s="4"/>
       <c r="DB77" s="4"/>
+      <c r="DC77" s="4"/>
     </row>
     <row r="78" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A78" s="3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="CX78" s="4"/>
       <c r="CY78" s="4"/>
       <c r="CZ78" s="4"/>
       <c r="DA78" s="4"/>
       <c r="DB78" s="4"/>
+      <c r="DC78" s="4"/>
     </row>
     <row r="79" spans="1:179" x14ac:dyDescent="0.2">
       <c r="CX79" s="4"/>
@@ -10607,6 +10659,7 @@
       <c r="CZ79" s="4"/>
       <c r="DA79" s="4"/>
       <c r="DB79" s="4"/>
+      <c r="DC79" s="4"/>
     </row>
     <row r="80" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A80" s="3" t="s">
@@ -10617,16 +10670,18 @@
       <c r="CZ80" s="4"/>
       <c r="DA80" s="4"/>
       <c r="DB80" s="4"/>
+      <c r="DC80" s="4"/>
     </row>
     <row r="81" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A81" s="3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="CX81" s="4"/>
       <c r="CY81" s="4"/>
       <c r="CZ81" s="4"/>
       <c r="DA81" s="4"/>
       <c r="DB81" s="4"/>
+      <c r="DC81" s="4"/>
     </row>
     <row r="82" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A82" s="3" t="s">
@@ -10637,6 +10692,7 @@
       <c r="CZ82" s="4"/>
       <c r="DA82" s="4"/>
       <c r="DB82" s="4"/>
+      <c r="DC82" s="4"/>
     </row>
     <row r="84" spans="1:179" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A84" s="16"/>
@@ -10799,6 +10855,7 @@
       <c r="DB84" s="20">
         <v>2026</v>
       </c>
+      <c r="DC84" s="20"/>
     </row>
     <row r="85" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A85" s="5" t="s">
@@ -11118,6 +11175,9 @@
       </c>
       <c r="DB85" s="12" t="s">
         <v>2</v>
+      </c>
+      <c r="DC85" s="12" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="86" spans="1:179" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
@@ -11440,9 +11500,11 @@
         <v>130.31635891990027</v>
       </c>
       <c r="DB87" s="15">
-        <v>135.64244603508024</v>
-      </c>
-      <c r="DC87" s="8"/>
+        <v>135.64244603508027</v>
+      </c>
+      <c r="DC87" s="15">
+        <v>137.53215537707234</v>
+      </c>
       <c r="DD87" s="8"/>
       <c r="DE87" s="8"/>
       <c r="DF87" s="8"/>
@@ -11833,9 +11895,11 @@
         <v>121.93988402904634</v>
       </c>
       <c r="DB88" s="15">
-        <v>123.58517557586259</v>
-      </c>
-      <c r="DC88" s="8"/>
+        <v>123.58497903745878</v>
+      </c>
+      <c r="DC88" s="15">
+        <v>124.7551768120186</v>
+      </c>
       <c r="DD88" s="8"/>
       <c r="DE88" s="8"/>
       <c r="DF88" s="8"/>
@@ -12406,9 +12470,11 @@
         <v>126.36365857630096</v>
       </c>
       <c r="DB90" s="15">
-        <v>129.60814951528002</v>
-      </c>
-      <c r="DC90" s="8"/>
+        <v>129.59893386851385</v>
+      </c>
+      <c r="DC90" s="15">
+        <v>131.32319695401594</v>
+      </c>
       <c r="DD90" s="8"/>
       <c r="DE90" s="8"/>
       <c r="DF90" s="8"/>
@@ -12589,6 +12655,7 @@
       <c r="CZ91" s="10"/>
       <c r="DA91" s="10"/>
       <c r="DB91" s="10"/>
+      <c r="DC91" s="10"/>
     </row>
     <row r="92" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A92" s="11" t="s">
@@ -12607,7 +12674,7 @@
     </row>
     <row r="97" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A97" s="3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="99" spans="1:179" x14ac:dyDescent="0.2">
@@ -12617,7 +12684,7 @@
     </row>
     <row r="100" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A100" s="3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="101" spans="1:179" x14ac:dyDescent="0.2">
@@ -12786,6 +12853,7 @@
       <c r="DB103" s="20">
         <v>2026</v>
       </c>
+      <c r="DC103" s="20"/>
     </row>
     <row r="104" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A104" s="5" t="s">
@@ -13105,6 +13173,9 @@
       </c>
       <c r="DB104" s="12" t="s">
         <v>2</v>
+      </c>
+      <c r="DC104" s="12" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="105" spans="1:179" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
@@ -13427,9 +13498,11 @@
         <v>54.463862824494647</v>
       </c>
       <c r="DB106" s="15">
-        <v>52.278760728663606</v>
-      </c>
-      <c r="DC106" s="8"/>
+        <v>52.203336832523995</v>
+      </c>
+      <c r="DC106" s="15">
+        <v>53.835544787129983</v>
+      </c>
       <c r="DD106" s="8"/>
       <c r="DE106" s="8"/>
       <c r="DF106" s="8"/>
@@ -13820,9 +13893,11 @@
         <v>45.536137175505367</v>
       </c>
       <c r="DB107" s="15">
-        <v>47.721239271336394</v>
-      </c>
-      <c r="DC107" s="8"/>
+        <v>47.796663167476019</v>
+      </c>
+      <c r="DC107" s="15">
+        <v>46.164455212870024</v>
+      </c>
       <c r="DD107" s="8"/>
       <c r="DE107" s="8"/>
       <c r="DF107" s="8"/>
@@ -14395,7 +14470,9 @@
       <c r="DB109" s="15">
         <v>100</v>
       </c>
-      <c r="DC109" s="8"/>
+      <c r="DC109" s="15">
+        <v>100</v>
+      </c>
       <c r="DD109" s="8"/>
       <c r="DE109" s="8"/>
       <c r="DF109" s="8"/>
@@ -14576,6 +14653,7 @@
       <c r="CZ110" s="10"/>
       <c r="DA110" s="10"/>
       <c r="DB110" s="10"/>
+      <c r="DC110" s="10"/>
     </row>
     <row r="111" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A111" s="11" t="s">
@@ -14954,7 +15032,7 @@
     </row>
     <row r="116" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A116" s="3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="118" spans="1:179" x14ac:dyDescent="0.2">
@@ -14964,7 +15042,7 @@
     </row>
     <row r="119" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A119" s="3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="120" spans="1:179" x14ac:dyDescent="0.2">
@@ -15133,6 +15211,7 @@
       <c r="DB122" s="20">
         <v>2026</v>
       </c>
+      <c r="DC122" s="20"/>
     </row>
     <row r="123" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A123" s="5" t="s">
@@ -15452,6 +15531,9 @@
       </c>
       <c r="DB123" s="12" t="s">
         <v>2</v>
+      </c>
+      <c r="DC123" s="12" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="124" spans="1:179" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
@@ -15774,9 +15856,11 @@
         <v>52.811888113994577</v>
       </c>
       <c r="DB125" s="15">
-        <v>49.953046668310733</v>
-      </c>
-      <c r="DC125" s="8"/>
+        <v>49.877431406127229</v>
+      </c>
+      <c r="DC125" s="15">
+        <v>51.405112003251674</v>
+      </c>
       <c r="DD125" s="8"/>
       <c r="DE125" s="8"/>
       <c r="DF125" s="8"/>
@@ -16167,9 +16251,11 @@
         <v>47.18811188600543</v>
       </c>
       <c r="DB126" s="15">
-        <v>50.046953331689267</v>
-      </c>
-      <c r="DC126" s="8"/>
+        <v>50.122568593872771</v>
+      </c>
+      <c r="DC126" s="15">
+        <v>48.594887996748326</v>
+      </c>
       <c r="DD126" s="8"/>
       <c r="DE126" s="8"/>
       <c r="DF126" s="8"/>
@@ -16742,7 +16828,9 @@
       <c r="DB128" s="15">
         <v>100</v>
       </c>
-      <c r="DC128" s="8"/>
+      <c r="DC128" s="15">
+        <v>100</v>
+      </c>
       <c r="DD128" s="8"/>
       <c r="DE128" s="8"/>
       <c r="DF128" s="8"/>
@@ -16923,6 +17011,7 @@
       <c r="CZ129" s="10"/>
       <c r="DA129" s="10"/>
       <c r="DB129" s="10"/>
+      <c r="DC129" s="10"/>
     </row>
     <row r="130" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A130" s="11" t="s">
@@ -17036,7 +17125,7 @@
       <c r="CZ131" s="24"/>
       <c r="DA131" s="24"/>
       <c r="DB131" s="24"/>
-      <c r="DC131" s="13"/>
+      <c r="DC131" s="24"/>
       <c r="DD131" s="13"/>
       <c r="DE131" s="13"/>
       <c r="DF131" s="13"/>
@@ -17111,11 +17200,12 @@
       <c r="FW131" s="13"/>
     </row>
     <row r="132" spans="1:179" x14ac:dyDescent="0.2">
-      <c r="CX132" s="4"/>
-      <c r="CY132" s="4"/>
-      <c r="CZ132" s="4"/>
-      <c r="DA132" s="4"/>
+      <c r="CX132" s="6"/>
+      <c r="CY132" s="6"/>
+      <c r="CZ132" s="6"/>
+      <c r="DA132" s="6"/>
       <c r="DB132" s="6"/>
+      <c r="DC132" s="6"/>
     </row>
     <row r="133" spans="1:179" x14ac:dyDescent="0.2">
       <c r="CT133" s="6"/>
@@ -17126,6 +17216,7 @@
       <c r="CZ133" s="6"/>
       <c r="DA133" s="6"/>
       <c r="DB133" s="6"/>
+      <c r="DC133" s="6"/>
     </row>
     <row r="134" spans="1:179" x14ac:dyDescent="0.2">
       <c r="CT134" s="6"/>
@@ -17135,15 +17226,13 @@
       <c r="CY134" s="6"/>
       <c r="CZ134" s="6"/>
       <c r="DA134" s="6"/>
+      <c r="DB134" s="6"/>
+      <c r="DC134" s="6"/>
     </row>
     <row r="135" spans="1:179" x14ac:dyDescent="0.2">
       <c r="CT135" s="6"/>
       <c r="CU135" s="6"/>
       <c r="CV135" s="6"/>
-      <c r="CX135" s="6"/>
-      <c r="CY135" s="6"/>
-      <c r="CZ135" s="6"/>
-      <c r="DA135" s="6"/>
     </row>
   </sheetData>
   <printOptions horizontalCentered="1"/>
@@ -17151,9 +17240,9 @@
   <pageSetup paperSize="9" scale="48" orientation="landscape" r:id="rId1"/>
   <headerFooter alignWithMargins="0"/>
   <rowBreaks count="3" manualBreakCount="3">
-    <brk id="38" max="105" man="1"/>
-    <brk id="76" max="105" man="1"/>
-    <brk id="94" max="105" man="1"/>
+    <brk id="38" max="106" man="1"/>
+    <brk id="76" max="106" man="1"/>
+    <brk id="94" max="106" man="1"/>
   </rowBreaks>
 </worksheet>
 </file>